--- a/research/traditional_assets/database/data/singapore/singapore_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.152</v>
+        <v>0.09720000000000001</v>
       </c>
       <c r="E2">
-        <v>0.24</v>
+        <v>0.12</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,34 +600,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.006168258333420495</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>0.005793742316494167</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>127.36</v>
+        <v>79.5</v>
       </c>
       <c r="L2">
-        <v>0.279506649694948</v>
+        <v>0.2222532848755941</v>
       </c>
       <c r="M2">
         <v>29.7</v>
       </c>
       <c r="N2">
-        <v>0.02486812358703843</v>
+        <v>0.032587228439763</v>
       </c>
       <c r="O2">
-        <v>0.2331972361809045</v>
+        <v>0.3735849056603773</v>
       </c>
       <c r="P2">
         <v>29.7</v>
       </c>
       <c r="Q2">
-        <v>0.02486812358703843</v>
+        <v>0.032587228439763</v>
       </c>
       <c r="R2">
-        <v>0.2331972361809045</v>
+        <v>0.3735849056603773</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,70 +636,61 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>386.6</v>
+        <v>785</v>
       </c>
       <c r="V2">
-        <v>0.3237042619107428</v>
+        <v>0.8613122668422207</v>
       </c>
       <c r="W2">
-        <v>-0.334044469695199</v>
+        <v>0.06336175978321511</v>
       </c>
       <c r="X2">
-        <v>0.0457497653634281</v>
+        <v>0.08797059791909774</v>
       </c>
       <c r="Y2">
-        <v>-0.3797942350586271</v>
+        <v>-0.02460883813588263</v>
       </c>
       <c r="Z2">
-        <v>0.2476298841637336</v>
+        <v>0.1396938217605249</v>
       </c>
       <c r="AA2">
-        <v>0.2876879067068994</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03363584339459663</v>
+        <v>0.06373700096127567</v>
       </c>
       <c r="AC2">
-        <v>0.2540520633123027</v>
+        <v>-0.06373700096127567</v>
       </c>
       <c r="AD2">
-        <v>1686.4</v>
+        <v>902.3</v>
       </c>
       <c r="AE2">
-        <v>0.03685703896808507</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>1686.436857038968</v>
+        <v>902.3</v>
       </c>
       <c r="AG2">
-        <v>1299.836857038968</v>
+        <v>117.3</v>
       </c>
       <c r="AH2">
-        <v>0.5854185719595406</v>
+        <v>0.4974913160941722</v>
       </c>
       <c r="AI2">
-        <v>0.5654560139500494</v>
+        <v>0.4138041733547351</v>
       </c>
       <c r="AJ2">
-        <v>0.5211569899905696</v>
+        <v>0.1140274132400116</v>
       </c>
       <c r="AK2">
-        <v>0.5007390404810232</v>
+        <v>0.08405589394482262</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.139</v>
-      </c>
-      <c r="AN2">
-        <v>44378.94736842105</v>
-      </c>
-      <c r="AP2">
-        <v>34206.23307997284</v>
-      </c>
-      <c r="AQ2">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Raffles Financial Group Limited (CNSX:RICH)</t>
+          <t>UOB-Kay Hian Holdings Limited (SGX:U10)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -718,6 +709,12 @@
           <t>Brokerage &amp; Investment Banking</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.09720000000000001</v>
+      </c>
+      <c r="E3">
+        <v>0.12</v>
+      </c>
       <c r="G3">
         <v>0</v>
       </c>
@@ -725,224 +722,96 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.5904681916399963</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>0.5904681916399963</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>-3.84</v>
+        <v>79.5</v>
       </c>
       <c r="L3">
-        <v>-0.8067226890756303</v>
+        <v>0.2222532848755941</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>29.7</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.032587228439763</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.3735849056603773</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>29.7</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.032587228439763</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.3735849056603773</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>16.5</v>
+        <v>785</v>
       </c>
       <c r="V3">
-        <v>0.09375</v>
+        <v>0.8613122668422207</v>
       </c>
       <c r="W3">
-        <v>-0.7836734693877551</v>
+        <v>0.06336175978321511</v>
       </c>
       <c r="X3">
-        <v>0.03326742668205729</v>
+        <v>0.08797059791909774</v>
       </c>
       <c r="Y3">
-        <v>-0.8169408960698124</v>
+        <v>-0.02460883813588263</v>
       </c>
       <c r="Z3">
-        <v>0.974439980950914</v>
+        <v>0.1396938217605249</v>
       </c>
       <c r="AA3">
-        <v>0.5753758134137987</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.03326585041450873</v>
+        <v>0.06373700096127567</v>
       </c>
       <c r="AC3">
-        <v>0.54210996299929</v>
+        <v>-0.06373700096127567</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>902.3</v>
       </c>
       <c r="AE3">
-        <v>0.03685703896808507</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.03685703896808507</v>
+        <v>902.3</v>
       </c>
       <c r="AG3">
-        <v>-16.46314296103192</v>
+        <v>117.3</v>
       </c>
       <c r="AH3">
-        <v>0.0002093711486789739</v>
+        <v>0.4974913160941722</v>
       </c>
       <c r="AI3">
-        <v>0.001383685729670189</v>
+        <v>0.4138041733547351</v>
       </c>
       <c r="AJ3">
-        <v>-0.1031933514711943</v>
+        <v>0.1140274132400116</v>
       </c>
       <c r="AK3">
-        <v>-1.624087515266748</v>
+        <v>0.08405589394482262</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.139</v>
-      </c>
-      <c r="AN3">
-        <v>0</v>
-      </c>
-      <c r="AP3">
-        <v>-433.240604237682</v>
-      </c>
-      <c r="AQ3">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>UOB-Kay Hian Holdings Limited (SGX:U10)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.152</v>
-      </c>
-      <c r="E4">
-        <v>0.24</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>131.2</v>
-      </c>
-      <c r="L4">
-        <v>0.2909736083388778</v>
-      </c>
-      <c r="M4">
-        <v>29.7</v>
-      </c>
-      <c r="N4">
-        <v>0.02916625748797015</v>
-      </c>
-      <c r="O4">
-        <v>0.2263719512195122</v>
-      </c>
-      <c r="P4">
-        <v>29.7</v>
-      </c>
-      <c r="Q4">
-        <v>0.02916625748797015</v>
-      </c>
-      <c r="R4">
-        <v>0.2263719512195122</v>
-      </c>
-      <c r="S4">
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>370.1</v>
-      </c>
-      <c r="V4">
-        <v>0.3634488853972307</v>
-      </c>
-      <c r="W4">
-        <v>0.1155845299973571</v>
-      </c>
-      <c r="X4">
-        <v>0.05823210404479892</v>
-      </c>
-      <c r="Y4">
-        <v>0.05735242595255814</v>
-      </c>
-      <c r="Z4">
-        <v>0.2456952920662598</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.03400583637468454</v>
-      </c>
-      <c r="AC4">
-        <v>-0.03400583637468454</v>
-      </c>
-      <c r="AD4">
-        <v>1686.4</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>1686.4</v>
-      </c>
-      <c r="AG4">
-        <v>1316.3</v>
-      </c>
-      <c r="AH4">
-        <v>0.623507228158391</v>
-      </c>
-      <c r="AI4">
-        <v>0.5705392787062724</v>
-      </c>
-      <c r="AJ4">
-        <v>0.5638224963591193</v>
-      </c>
-      <c r="AK4">
-        <v>0.5090691108790657</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/singapore/singapore_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_brokerage_investment_banking.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.09720000000000001</v>
+        <v>0.0594</v>
       </c>
       <c r="E2">
-        <v>0.12</v>
+        <v>0.0682</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>79.5</v>
+        <v>88.3</v>
       </c>
       <c r="L2">
-        <v>0.2222532848755941</v>
+        <v>0.2432506887052341</v>
       </c>
       <c r="M2">
-        <v>29.7</v>
+        <v>26.56</v>
       </c>
       <c r="N2">
-        <v>0.032587228439763</v>
+        <v>0.02906862208602386</v>
       </c>
       <c r="O2">
-        <v>0.3735849056603773</v>
+        <v>0.3007927519818799</v>
       </c>
       <c r="P2">
-        <v>29.7</v>
+        <v>19</v>
       </c>
       <c r="Q2">
-        <v>0.032587228439763</v>
+        <v>0.02079457152238152</v>
       </c>
       <c r="R2">
-        <v>0.3735849056603773</v>
+        <v>0.2151755379388449</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>7.559999999999999</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.2846385542168675</v>
       </c>
       <c r="U2">
-        <v>785</v>
+        <v>754</v>
       </c>
       <c r="V2">
-        <v>0.8613122668422207</v>
+        <v>0.8252161540987194</v>
       </c>
       <c r="W2">
-        <v>0.06336175978321511</v>
+        <v>0.06985206866545368</v>
       </c>
       <c r="X2">
-        <v>0.08797059791909774</v>
+        <v>0.07061921146129445</v>
       </c>
       <c r="Y2">
-        <v>-0.02460883813588263</v>
+        <v>-0.0007671427958407667</v>
       </c>
       <c r="Z2">
-        <v>0.1396938217605249</v>
+        <v>0.2645464085820896</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06373700096127567</v>
+        <v>0.05444685898482118</v>
       </c>
       <c r="AC2">
-        <v>-0.06373700096127567</v>
+        <v>-0.05444685898482118</v>
       </c>
       <c r="AD2">
-        <v>902.3</v>
+        <v>866.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>902.3</v>
+        <v>866.1</v>
       </c>
       <c r="AG2">
-        <v>117.3</v>
+        <v>112.1</v>
       </c>
       <c r="AH2">
-        <v>0.4974913160941722</v>
+        <v>0.4866277109787616</v>
       </c>
       <c r="AI2">
-        <v>0.4138041733547351</v>
+        <v>0.3899945965417867</v>
       </c>
       <c r="AJ2">
-        <v>0.1140274132400116</v>
+        <v>0.1092805615129655</v>
       </c>
       <c r="AK2">
-        <v>0.08405589394482262</v>
+        <v>0.07642487046632125</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.09720000000000001</v>
+        <v>0.0594</v>
       </c>
       <c r="E3">
-        <v>0.12</v>
+        <v>0.0682</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,85 +728,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>79.5</v>
+        <v>88.3</v>
       </c>
       <c r="L3">
-        <v>0.2222532848755941</v>
+        <v>0.2432506887052341</v>
       </c>
       <c r="M3">
-        <v>29.7</v>
+        <v>26.56</v>
       </c>
       <c r="N3">
-        <v>0.032587228439763</v>
+        <v>0.02906862208602386</v>
       </c>
       <c r="O3">
-        <v>0.3735849056603773</v>
+        <v>0.3007927519818799</v>
       </c>
       <c r="P3">
-        <v>29.7</v>
+        <v>19</v>
       </c>
       <c r="Q3">
-        <v>0.032587228439763</v>
+        <v>0.02079457152238152</v>
       </c>
       <c r="R3">
-        <v>0.3735849056603773</v>
+        <v>0.2151755379388449</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>7.559999999999999</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.2846385542168675</v>
       </c>
       <c r="U3">
-        <v>785</v>
+        <v>754</v>
       </c>
       <c r="V3">
-        <v>0.8613122668422207</v>
+        <v>0.8252161540987194</v>
       </c>
       <c r="W3">
-        <v>0.06336175978321511</v>
+        <v>0.06985206866545368</v>
       </c>
       <c r="X3">
-        <v>0.08797059791909774</v>
+        <v>0.07061921146129445</v>
       </c>
       <c r="Y3">
-        <v>-0.02460883813588263</v>
+        <v>-0.0007671427958407667</v>
       </c>
       <c r="Z3">
-        <v>0.1396938217605249</v>
+        <v>0.2645464085820896</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06373700096127567</v>
+        <v>0.05444685898482118</v>
       </c>
       <c r="AC3">
-        <v>-0.06373700096127567</v>
+        <v>-0.05444685898482118</v>
       </c>
       <c r="AD3">
-        <v>902.3</v>
+        <v>866.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>902.3</v>
+        <v>866.1</v>
       </c>
       <c r="AG3">
-        <v>117.3</v>
+        <v>112.1</v>
       </c>
       <c r="AH3">
-        <v>0.4974913160941722</v>
+        <v>0.4866277109787616</v>
       </c>
       <c r="AI3">
-        <v>0.4138041733547351</v>
+        <v>0.3899945965417867</v>
       </c>
       <c r="AJ3">
-        <v>0.1140274132400116</v>
+        <v>0.1092805615129655</v>
       </c>
       <c r="AK3">
-        <v>0.08405589394482262</v>
+        <v>0.07642487046632125</v>
       </c>
       <c r="AL3">
         <v>0</v>
